--- a/artfynd/A 61663-2021 artfynd.xlsx
+++ b/artfynd/A 61663-2021 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>126407907</v>
       </c>
       <c r="B3" t="n">
-        <v>91262</v>
+        <v>91265</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
